--- a/example.xlsx
+++ b/example.xlsx
@@ -482,20 +482,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <f>2364.012877/10</f>
-        <v>236.40128770000001</v>
+        <f>2364.012877</f>
+        <v>2364.0128770000001</v>
       </c>
       <c r="C6" s="3">
-        <f>2294.8135/10</f>
-        <v>229.48135000000002</v>
+        <f>2294.8135</f>
+        <v>2294.8135000000002</v>
       </c>
       <c r="D6" s="3">
-        <f>2303.336/10</f>
-        <v>230.33359999999999</v>
+        <f>2303.336</f>
+        <v>2303.3359999999998</v>
       </c>
       <c r="E6" s="3">
-        <f>2250.0352/10</f>
-        <v>225.00351999999998</v>
+        <f>2250.0352</f>
+        <v>2250.0351999999998</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
